--- a/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:30:17+00:00</t>
+    <t>2025-10-07T21:05:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:05:34+00:00</t>
+    <t>2025-11-21T23:55:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T23:55:27+00:00</t>
+    <t>2026-01-12T21:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T21:43:07+00:00</t>
+    <t>2026-01-22T19:20:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T19:20:19+00:00</t>
+    <t>2026-02-17T21:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T21:23:45+00:00</t>
+    <t>2026-03-17T18:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
+++ b/release-branch/ValueSet-bc-contact-point-system-value-set.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T18:19:20+00:00</t>
+    <t>2026-03-25T21:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
